--- a/data/06_qualitative.xlsx
+++ b/data/06_qualitative.xlsx
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="H2" s="3" t="n">
-        <v>73.54000000000001</v>
+        <v>75.84</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>1</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>69.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>77.2</v>
+        <v>79.5</v>
       </c>
       <c r="L2" s="5" t="n">
         <v>1</v>
@@ -652,16 +652,16 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>72.08</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="I3" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>66.8</v>
+        <v>67.8</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>77.3</v>
+        <v>78.3</v>
       </c>
       <c r="L3" s="5" t="n">
         <v>2</v>
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>68.67</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>3</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>63.4</v>
+        <v>64.8</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>73.90000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="L4" s="5" t="n">
         <v>1</v>
@@ -724,25 +724,25 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>GHA</t>
+          <t>NAM</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="3" t="n">
-        <v>97</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
@@ -750,22 +750,22 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>64.37</v>
+        <v>65.84</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>4</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>61.6</v>
+        <v>60.6</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>67.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>64.3</v>
+        <v>65.34</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>5</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>61.5</v>
+        <v>62.5</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M6" s="5" t="n">
         <v>16</v>
@@ -818,17 +818,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>NAM</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr"/>
@@ -844,22 +844,22 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>64.12</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>6</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>58.9</v>
+        <v>59.8</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="L7" s="5" t="n">
         <v>1</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -891,16 +891,16 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>63.68</v>
+        <v>64.41</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>7</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>57.6</v>
+        <v>58.4</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>69.7</v>
+        <v>70.5</v>
       </c>
       <c r="L8" s="5" t="n">
         <v>2</v>
@@ -912,25 +912,25 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>GHA</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
@@ -938,131 +938,131 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>62.9</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>8</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>57.7</v>
+        <v>61.3</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>STP</t>
+          <t>RWA</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Sao Tome &amp; Principe</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Islands</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="3" t="n">
-        <v>93.90000000000001</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>Good</t>
+        <v>5</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>62.2</v>
+        <v>62.38</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>58.6</v>
+        <v>56.3</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>65.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>RWA</t>
+          <t>STP</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Sao Tome &amp; Principe</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>East</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr"/>
+          <t>Islands</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="E11" s="3" t="n">
-        <v>84.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>1</v>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>61.57</v>
+        <v>61.88</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>10</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>55.5</v>
+        <v>59.1</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>67.59999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>EGY</t>
+          <t>TUN</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1072,27 +1072,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="3" t="n">
-        <v>100</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>Excellent</t>
+        <v>4</v>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>59.74</v>
+        <v>61.06</v>
       </c>
       <c r="I12" s="5" t="n">
         <v>11</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>57.7</v>
+        <v>55.8</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>61.7</v>
+        <v>66.3</v>
       </c>
       <c r="L12" s="5" t="n">
         <v>2</v>
@@ -1104,12 +1104,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>DZA</t>
+          <t>EGY</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1119,27 +1119,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="3" t="n">
-        <v>81.8</v>
+        <v>100</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>0</v>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Excellent</t>
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>59.08</v>
+        <v>60.82</v>
       </c>
       <c r="I13" s="5" t="n">
         <v>12</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>52.2</v>
+        <v>58.8</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>62.8</v>
       </c>
       <c r="L13" s="5" t="n">
         <v>3</v>
@@ -1151,111 +1151,111 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>TUN</t>
+          <t>ZAF</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>Good</t>
+        <v>0</v>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Excellent</t>
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>58.87</v>
+        <v>60.71</v>
       </c>
       <c r="I14" s="5" t="n">
         <v>13</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>53.6</v>
+        <v>58.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>62.7</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ZAF</t>
+          <t>DZA</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="3" t="n">
-        <v>100</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>Excellent</t>
+        <v>5</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>57.78</v>
+        <v>59.5</v>
       </c>
       <c r="I15" s="5" t="n">
         <v>14</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>55.8</v>
+        <v>53.5</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>59.8</v>
+        <v>65.5</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GMB</t>
+          <t>KEN</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>The Gambia</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
@@ -1271,33 +1271,33 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>57.38</v>
+        <v>57.05</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>15</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>52.1</v>
+        <v>51.8</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>62.6</v>
+        <v>62.3</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>BEN</t>
+          <t>GMB</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>The Gambia</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1307,10 +1307,10 @@
       </c>
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="3" t="n">
-        <v>97</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
@@ -1318,19 +1318,19 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>56.37</v>
+        <v>56.69</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>16</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>53.6</v>
+        <v>51.5</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>59.2</v>
+        <v>61.9</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>16</v>
@@ -1339,12 +1339,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>CIV</t>
+          <t>BEN</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1354,10 +1354,10 @@
       </c>
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="3" t="n">
-        <v>93.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>56.18</v>
+        <v>56</v>
       </c>
       <c r="I18" s="5" t="n">
         <v>17</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>52.6</v>
+        <v>53.2</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>59.8</v>
+        <v>58.8</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M18" s="5" t="n">
         <v>16</v>
@@ -1386,25 +1386,25 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>KEN</t>
+          <t>CIV</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Cote d'Ivoire</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
@@ -1412,22 +1412,22 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>56.04</v>
+        <v>55.88</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>18</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>50.8</v>
+        <v>52.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>61.3</v>
+        <v>59.5</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -1459,16 +1459,16 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>55.84</v>
+        <v>55.32</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>19</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>52.2</v>
+        <v>51.7</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>59.5</v>
+        <v>58.9</v>
       </c>
       <c r="L20" s="5" t="n">
         <v>4</v>
@@ -1480,12 +1480,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>ZMB</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1495,10 +1495,10 @@
       </c>
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>54.28</v>
+        <v>53.92</v>
       </c>
       <c r="I21" s="5" t="n">
         <v>20</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>49</v>
+        <v>49.5</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>59.5</v>
+        <v>58.3</v>
       </c>
       <c r="L21" s="5" t="n">
         <v>3</v>
@@ -1527,12 +1527,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>MWI</t>
+          <t>ZMB</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1553,16 +1553,16 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>54.01</v>
+        <v>53.53</v>
       </c>
       <c r="I22" s="5" t="n">
         <v>21</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>48.8</v>
+        <v>48.3</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>59.2</v>
+        <v>58.8</v>
       </c>
       <c r="L22" s="5" t="n">
         <v>4</v>
@@ -1574,12 +1574,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>MWI</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1589,10 +1589,10 @@
       </c>
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>53.84</v>
+        <v>52.99</v>
       </c>
       <c r="I23" s="5" t="n">
         <v>22</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>49.4</v>
+        <v>47.8</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>58.3</v>
+        <v>58.2</v>
       </c>
       <c r="L23" s="5" t="n">
         <v>5</v>
@@ -1621,76 +1621,76 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GAB</t>
+          <t>COM</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Central</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr"/>
+          <t>Islands</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="E24" s="3" t="n">
-        <v>78.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>2</v>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>53.24</v>
+        <v>52.87</v>
       </c>
       <c r="I24" s="5" t="n">
         <v>23</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>45.6</v>
+        <v>49.3</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>60.9</v>
+        <v>56.5</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>COM</t>
+          <t>TGO</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Islands</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
@@ -1698,38 +1698,38 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>52.59</v>
+        <v>52.82</v>
       </c>
       <c r="I25" s="5" t="n">
         <v>24</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>48.2</v>
+        <v>49.2</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>57</v>
+        <v>56.4</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>TGO</t>
+          <t>TZA</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
@@ -1745,38 +1745,38 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>52.47</v>
+        <v>52.73</v>
       </c>
       <c r="I26" s="5" t="n">
         <v>25</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>48.9</v>
+        <v>49.1</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>56.1</v>
+        <v>56.3</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>TZA</t>
+          <t>SWZ</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr"/>
@@ -1792,93 +1792,93 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>52.27</v>
+        <v>51.87</v>
       </c>
       <c r="I27" s="5" t="n">
         <v>26</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>48.7</v>
+        <v>48.3</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>55.9</v>
+        <v>55.5</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>SWZ</t>
+          <t>DJI</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Djibouti</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="3" t="n">
-        <v>93.90000000000001</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>Good</t>
+        <v>5</v>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>51.18</v>
+        <v>51.08</v>
       </c>
       <c r="I28" s="5" t="n">
         <v>27</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>47.6</v>
+        <v>45</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>54.8</v>
+        <v>57.1</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>DJI</t>
+          <t>GAB</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Djibouti</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="3" t="n">
-        <v>84.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
@@ -1886,33 +1886,33 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>50.64</v>
+        <v>50.95</v>
       </c>
       <c r="I29" s="5" t="n">
         <v>28</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>44.6</v>
+        <v>44.1</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>56.7</v>
+        <v>57.8</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>SLE</t>
+          <t>MRT</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Mauritania</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1922,10 +1922,10 @@
       </c>
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="3" t="n">
-        <v>93.90000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
@@ -1933,16 +1933,16 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>50.43</v>
+        <v>50.79</v>
       </c>
       <c r="I30" s="5" t="n">
         <v>29</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>46.8</v>
+        <v>45.6</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L30" s="5" t="n">
         <v>8</v>
@@ -1954,12 +1954,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>MRT</t>
+          <t>SLE</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Mauritania</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1969,10 +1969,10 @@
       </c>
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
@@ -1980,16 +1980,16 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>50.42</v>
+        <v>50.37</v>
       </c>
       <c r="I31" s="5" t="n">
         <v>30</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>45.2</v>
+        <v>46.7</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>55.7</v>
+        <v>54</v>
       </c>
       <c r="L31" s="5" t="n">
         <v>9</v>
@@ -2031,16 +2031,16 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>49.07</v>
+        <v>49.32</v>
       </c>
       <c r="I32" s="5" t="n">
         <v>31</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>46.3</v>
+        <v>46.5</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>51.9</v>
+        <v>52.1</v>
       </c>
       <c r="L32" s="5" t="n">
         <v>5</v>
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>47.72</v>
+        <v>47.75</v>
       </c>
       <c r="I33" s="5" t="n">
         <v>32</v>
@@ -2099,72 +2099,72 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>LBR</t>
+          <t>BDI</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="3" t="n">
-        <v>84.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>1</v>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>46.63</v>
+        <v>47.28</v>
       </c>
       <c r="I34" s="5" t="n">
         <v>33</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>40.6</v>
+        <v>44.5</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>52.7</v>
+        <v>50.1</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>BDI</t>
+          <t>BFA</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="3" t="n">
-        <v>97</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
@@ -2172,22 +2172,22 @@
         </is>
       </c>
       <c r="H35" s="3" t="n">
-        <v>46.34</v>
+        <v>47.22</v>
       </c>
       <c r="I35" s="5" t="n">
         <v>34</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>43.5</v>
+        <v>43.6</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>49.2</v>
+        <v>50.8</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36">
@@ -2208,10 +2208,10 @@
       </c>
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="3" t="n">
-        <v>75.8</v>
+        <v>78.8</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
@@ -2219,16 +2219,16 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>46.27</v>
+        <v>46.19</v>
       </c>
       <c r="I36" s="5" t="n">
         <v>35</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>37.8</v>
+        <v>38.5</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>54.7</v>
+        <v>53.9</v>
       </c>
       <c r="L36" s="5" t="n">
         <v>12</v>
@@ -2240,12 +2240,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>BFA</t>
+          <t>LBR</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2255,27 +2255,27 @@
       </c>
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="3" t="n">
-        <v>93.90000000000001</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>Good</t>
+        <v>5</v>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H37" s="3" t="n">
-        <v>46.04</v>
+        <v>45.92</v>
       </c>
       <c r="I37" s="5" t="n">
         <v>36</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>42.4</v>
+        <v>39.9</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>49.7</v>
+        <v>52</v>
       </c>
       <c r="L37" s="5" t="n">
         <v>13</v>
@@ -2287,25 +2287,25 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>CMR</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="3" t="n">
-        <v>97</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
@@ -2313,46 +2313,46 @@
         </is>
       </c>
       <c r="H38" s="3" t="n">
-        <v>45.75</v>
+        <v>45.9</v>
       </c>
       <c r="I38" s="5" t="n">
         <v>37</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>42.9</v>
+        <v>42.3</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>48.6</v>
+        <v>49.5</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>MOZ</t>
+          <t>CMR</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
@@ -2360,80 +2360,80 @@
         </is>
       </c>
       <c r="H39" s="3" t="n">
-        <v>45.56</v>
+        <v>45.74</v>
       </c>
       <c r="I39" s="5" t="n">
         <v>38</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>40.3</v>
+        <v>42.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>50.8</v>
+        <v>48.5</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>COG</t>
+          <t>LBY</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Republic of Congo</t>
+          <t>Libya</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="3" t="n">
-        <v>81.8</v>
+        <v>66.7</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>11</v>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>Caution</t>
         </is>
       </c>
       <c r="H40" s="3" t="n">
-        <v>45.5</v>
+        <v>45.03</v>
       </c>
       <c r="I40" s="5" t="n">
         <v>39</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>38.6</v>
+        <v>34.1</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>52.4</v>
+        <v>55.9</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>MOZ</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2443,10 +2443,10 @@
       </c>
       <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="3" t="n">
-        <v>93.90000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
@@ -2454,16 +2454,16 @@
         </is>
       </c>
       <c r="H41" s="3" t="n">
-        <v>45.47</v>
+        <v>44.96</v>
       </c>
       <c r="I41" s="5" t="n">
         <v>40</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>41.9</v>
+        <v>39.7</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>49.1</v>
+        <v>50.2</v>
       </c>
       <c r="L41" s="5" t="n">
         <v>10</v>
@@ -2475,12 +2475,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>AGO</t>
+          <t>COG</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Republic of Congo</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2490,10 +2490,10 @@
       </c>
       <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="3" t="n">
-        <v>84.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
@@ -2501,19 +2501,19 @@
         </is>
       </c>
       <c r="H42" s="3" t="n">
-        <v>44.83</v>
+        <v>44.73</v>
       </c>
       <c r="I42" s="5" t="n">
         <v>41</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>38.8</v>
+        <v>37.9</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>50.9</v>
+        <v>51.6</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M42" s="5" t="n">
         <v>8</v>
@@ -2522,95 +2522,95 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>LBY</t>
+          <t>MLI</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Libya</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="3" t="n">
-        <v>63.6</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t>Caution</t>
+        <v>4</v>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
         </is>
       </c>
       <c r="H43" s="3" t="n">
-        <v>44.82</v>
+        <v>44.7</v>
       </c>
       <c r="I43" s="5" t="n">
         <v>42</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>33.1</v>
+        <v>39.5</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>56.5</v>
+        <v>49.9</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>MLI</t>
+          <t>AGO</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>Good</t>
+        <v>5</v>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H44" s="3" t="n">
-        <v>44</v>
+        <v>44.07</v>
       </c>
       <c r="I44" s="5" t="n">
         <v>43</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>38.8</v>
+        <v>38</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>49.2</v>
+        <v>50.1</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
@@ -2642,16 +2642,16 @@
         </is>
       </c>
       <c r="H45" s="3" t="n">
-        <v>43.83</v>
+        <v>43.32</v>
       </c>
       <c r="I45" s="5" t="n">
         <v>44</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>38.6</v>
+        <v>38.1</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>49.1</v>
+        <v>48.6</v>
       </c>
       <c r="L45" s="5" t="n">
         <v>11</v>
@@ -2689,16 +2689,16 @@
         </is>
       </c>
       <c r="H46" s="3" t="n">
-        <v>42.64</v>
+        <v>42.45</v>
       </c>
       <c r="I46" s="5" t="n">
         <v>45</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>47.1</v>
+        <v>46.9</v>
       </c>
       <c r="L46" s="5" t="n">
         <v>15</v>
@@ -2736,16 +2736,16 @@
         </is>
       </c>
       <c r="H47" s="3" t="n">
-        <v>39.72</v>
+        <v>39.54</v>
       </c>
       <c r="I47" s="5" t="n">
         <v>46</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>35.3</v>
+        <v>35.1</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
       <c r="L47" s="5" t="n">
         <v>16</v>
@@ -2757,95 +2757,95 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GNQ</t>
+          <t>ERI</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Equatorial Guinea</t>
+          <t>Eritrea</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="3" t="n">
-        <v>72.7</v>
+        <v>60.6</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G48" s="6" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>13</v>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>Caution</t>
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>37.73</v>
+        <v>38.12</v>
       </c>
       <c r="I48" s="5" t="n">
         <v>47</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>28.5</v>
+        <v>25.6</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>47</v>
+        <v>50.6</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M48" s="5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>ERI</t>
+          <t>GNQ</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Eritrea</t>
+          <t>Equatorial Guinea</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="3" t="n">
-        <v>57.6</v>
+        <v>72.7</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="G49" s="8" t="inlineStr">
-        <is>
-          <t>Caution</t>
+        <v>9</v>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H49" s="3" t="n">
-        <v>35.43</v>
+        <v>34.9</v>
       </c>
       <c r="I49" s="5" t="n">
         <v>48</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>22.1</v>
+        <v>25.6</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>48.8</v>
+        <v>44.2</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M49" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50">
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="H50" s="3" t="n">
-        <v>34.74</v>
+        <v>34.78</v>
       </c>
       <c r="I50" s="5" t="n">
         <v>49</v>
@@ -2886,7 +2886,7 @@
         <v>26.3</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="L50" s="5" t="n">
         <v>6</v>
@@ -2924,16 +2924,16 @@
         </is>
       </c>
       <c r="H51" s="3" t="n">
-        <v>33.37</v>
+        <v>33.55</v>
       </c>
       <c r="I51" s="5" t="n">
         <v>50</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>28.9</v>
+        <v>29.1</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>37.8</v>
+        <v>38</v>
       </c>
       <c r="L51" s="5" t="n">
         <v>6</v>
@@ -2971,16 +2971,16 @@
         </is>
       </c>
       <c r="H52" s="3" t="n">
-        <v>30.67</v>
+        <v>30.53</v>
       </c>
       <c r="I52" s="5" t="n">
         <v>51</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>27.9</v>
+        <v>27.7</v>
       </c>
       <c r="K52" s="3" t="n">
-        <v>33.5</v>
+        <v>33.3</v>
       </c>
       <c r="L52" s="5" t="n">
         <v>7</v>
@@ -2992,95 +2992,95 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Central African Republic</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
       <c r="E53" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G53" s="4" t="inlineStr">
-        <is>
-          <t>Good</t>
+        <v>10</v>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>Caution</t>
         </is>
       </c>
       <c r="H53" s="3" t="n">
-        <v>28.39</v>
+        <v>27.48</v>
       </c>
       <c r="I53" s="5" t="n">
         <v>52</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>24</v>
+        <v>17.4</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>32.8</v>
+        <v>37.6</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Central African Republic</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="3" t="n">
-        <v>66.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G54" s="8" t="inlineStr">
-        <is>
-          <t>Caution</t>
+        <v>3</v>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
         </is>
       </c>
       <c r="H54" s="3" t="n">
-        <v>28.2</v>
+        <v>27.23</v>
       </c>
       <c r="I54" s="5" t="n">
         <v>53</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>17.3</v>
+        <v>22.8</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>39.1</v>
+        <v>31.7</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M54" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55">
@@ -3112,16 +3112,16 @@
         </is>
       </c>
       <c r="H55" s="3" t="n">
-        <v>20.34</v>
+        <v>17.77</v>
       </c>
       <c r="I55" s="5" t="n">
         <v>54</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>12.7</v>
+        <v>10.1</v>
       </c>
       <c r="K55" s="3" t="n">
-        <v>28</v>
+        <v>25.4</v>
       </c>
       <c r="L55" s="5" t="n">
         <v>14</v>
@@ -3930,12 +3930,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Firms with at least 10% foreign ownership (% of firms)</t>
+          <t>Domestic credit to private sector (% of GDP)</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>IC.FRM.FO.ZS</t>
+          <t>FS.AST.PRVT.GD.ZS</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -3969,14 +3969,14 @@
         </is>
       </c>
       <c r="I12" s="5" t="n">
-        <v>2010</v>
+        <v>2000</v>
       </c>
       <c r="J12" s="5" t="n">
         <v>2024</v>
       </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>Foreign ownership signals that the investment climate is sufficiently stable and open to attract external capital. Extended year range used because this is drawn from enterprise surveys conducted every few years.</t>
+          <t>Domestic credit to the private sector measures financial-sector depth: the extent to which banks and other institutions channel savings into productive private investment. Deep credit markets let firms and households absorb shocks without distress sales or default cascades, which is the economic-resilience channel most directly tied to stability. Replaces firm_foreign_owned (IC.FRM.FO.ZS) in the 2026 revision for three reasons (see methodology/METHODOLOGY_REVIEW.md C3): (1) firm_foreign_owned was the only indicator in the index with a NEGATIVE item-rest correlation (-0.10), meaning it moved against the rest of Pillar B as polarised; (2) it drew on enterprise surveys so infrequent that 20 of 49 countries carried pre-2021 values, some from 2006; (3) it is conceptually confounded in the African context, because extractive-sector FDI concentrates in less stable states, so high foreign ownership can signal resource dependence rather than a healthy investment climate. Coverage screened before adoption: 53/54 countries, 51 of them 2018 or later, median year 2024. Source: World Bank WDI FS.AST.PRVT.GD.ZS (IMF International Financial Statistics).</t>
         </is>
       </c>
     </row>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>Gender Parity Index = girls enrolled / boys enrolled. Values at 1.0 indicate parity; values below signal systematic exclusion of girls from primary education. GPI is conceptually distinct from enrollment level: a country with 70% primary enrollment and GPI of 0.6 has a different social profile than one with 70% enrollment and GPI of 1.0. UNESCO uses GPI as its primary gender equity metric in education (UNESCO 2022 Global Education Monitoring Report). Note: SE.ENR.PRIM.FM.ZS is the gross GPI; net GPI (SE.PRM.GINT.FM.ZS) has sparse African coverage and was not used. Source: World Bank WDI, UNESCO UIS.</t>
+          <t>Gender Parity Index = girls enrolled / boys enrolled. GPI is an equality measure whose ideal is exactly 1.0, so deviation in EITHER direction indicates dysfunction. The index therefore applies transform: distance_from_parity, min(GPI, 2 - GPI), before normalisation, and scores the result with positive polarity so that 1.0 is best. Prior to the 2026 revision this indicator was scored monotonically, which meant a country where boys were dropping out (GPI up to 1.16 in this sample; 17 of 54 countries exceed 1.0) scored HIGHER than a country at perfect parity — rewarding the opposite of the intended signal. UNESCO treats |GPI - 1| as the inequity measure for the same reason (UNESCO 2022 Global Education Monitoring Report). GPI is conceptually distinct from enrollment level: a country with 70% enrollment and GPI 0.6 has a different social profile than one with 70% enrollment and GPI 1.0. Note: SE.ENR.PRIM.FM.ZS is the gross GPI; net GPI (SE.PRM.GINT.FM.ZS) has sparse African coverage and was not used. Source: World Bank WDI, UNESCO UIS.</t>
         </is>
       </c>
     </row>
@@ -4294,7 +4294,7 @@
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>Secondary GPI captures whether girls progress beyond primary schooling at the same rate as boys. Persistent gaps at secondary level signal structural gender inequality with compounding consequences: female secondary enrollment is the strongest predictor of fertility rates, maternal health outcomes, and intergenerational poverty (UNESCO 2022). This is conceptually distinct from primary_gpi: in many African countries, primary GPI is near 1.0 while secondary GPI drops sharply (early marriage, economic constraints, safety), making secondary-level parity a more discriminating stability signal. Source: World Bank WDI SE.ENR.SECO.FM.ZS, UNESCO UIS.</t>
+          <t>Secondary GPI captures whether girls progress beyond primary schooling at the same rate as boys. Persistent gaps at secondary level signal structural gender inequality with compounding consequences: female secondary enrollment is the strongest predictor of fertility rates, maternal health outcomes, and intergenerational poverty (UNESCO 2022). Scored via transform: distance_from_parity, min(GPI, 2 - GPI), so that 1.0 is best and deviation in either direction is penalised; 25 of 54 countries in this sample exceed 1.0, and under the previous monotonic scoring their male-disadvantage gaps were rewarded. This is conceptually distinct from primary_gpi: in many African countries primary GPI is near 1.0 while secondary GPI drops sharply (early marriage, economic constraints, safety), making secondary-level parity a more discriminating stability signal. Source: World Bank WDI SE.ENR.SECO.FM.ZS, UNESCO UIS.</t>
         </is>
       </c>
     </row>
